--- a/データGUI07/Excel/連表2.xlsx
+++ b/データGUI07/Excel/連表2.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SVN\svn_nxt_development\trunk\Ver.7.0.0.0\06_総合試験\02_個別総合試験\旧ファイル変換\旧ファイル\V2.8.2\成果物\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\成果物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62030B80-2C49-417F-AD4C-D799FDFA4D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09ACAAF6-90B9-419C-A744-AB6AEEB5043D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="A" sheetId="1" r:id="rId1"/>
+    <sheet name="B" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
   <si>
     <t>自タグ</t>
     <rPh sb="0" eb="1">
@@ -58,6 +59,58 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>B001-001のテキスト</t>
+  </si>
+  <si>
+    <t>B001-001のサブテキスト</t>
+  </si>
+  <si>
+    <t>B001-004のサブテキスト</t>
+  </si>
+  <si>
+    <t>B001-005のサブテキスト</t>
+  </si>
+  <si>
+    <t>B001-006のテキスト</t>
+  </si>
+  <si>
+    <t>B001-006のサブテキスト</t>
+  </si>
+  <si>
+    <t>B001-007のテキスト</t>
+  </si>
+  <si>
+    <t>B001-007のサブテキスト</t>
+  </si>
+  <si>
+    <t>B001-008のテキスト</t>
+  </si>
+  <si>
+    <t>B001-008のサブテキスト</t>
+  </si>
+  <si>
+    <t>B001-009のテキスト</t>
+  </si>
+  <si>
+    <t>B001-009のサブテキスト</t>
+  </si>
+  <si>
+    <t>B001-001のテキスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B001-003のサブテキスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【B001-001】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【A001-001】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>【A001-002】</t>
   </si>
   <si>
@@ -85,97 +138,31 @@
     <t>【A001-010】</t>
   </si>
   <si>
-    <t>【B001-001】</t>
-  </si>
-  <si>
-    <t>B001-001のテキスト</t>
-  </si>
-  <si>
-    <t>B001-001のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-002】</t>
   </si>
   <si>
-    <t>B001-002のテキスト</t>
-  </si>
-  <si>
-    <t>B001-002のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-003】</t>
   </si>
   <si>
-    <t>B001-003のテキスト</t>
-  </si>
-  <si>
-    <t>B001-003のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-004】</t>
   </si>
   <si>
-    <t>B001-004のテキスト</t>
-  </si>
-  <si>
-    <t>B001-004のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-005】</t>
   </si>
   <si>
-    <t>B001-005のテキスト</t>
-  </si>
-  <si>
-    <t>B001-005のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-006】</t>
   </si>
   <si>
-    <t>B001-006のテキスト</t>
-  </si>
-  <si>
-    <t>B001-006のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-007】</t>
   </si>
   <si>
-    <t>B001-007のテキスト</t>
-  </si>
-  <si>
-    <t>B001-007のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-008】</t>
   </si>
   <si>
-    <t>B001-008のテキスト</t>
-  </si>
-  <si>
-    <t>B001-008のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-009】</t>
   </si>
   <si>
-    <t>B001-009のテキスト</t>
-  </si>
-  <si>
-    <t>B001-009のサブテキスト</t>
-  </si>
-  <si>
     <t>【B001-010】</t>
-  </si>
-  <si>
-    <t>B001-010のテキスト</t>
-  </si>
-  <si>
-    <t>B001-010のサブテキスト</t>
-  </si>
-  <si>
-    <t>【A001-001】</t>
   </si>
 </sst>
 </file>
@@ -222,7 +209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -524,142 +511,313 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
         <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6877C8B0-6336-42BC-8BD5-2614597AEEBD}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
         <v>12</v>
       </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
